--- a/output/pms/Lập_trình_Python/Session 04 - Toán tử số học, logic và Cấu trúc rẽ nhánh/Lesson 03 - Cấu trúc rẽ nhánh điều khiển với if, elif và else/Câu hỏi Quizz/Quizz_Session04_Lesson03.xlsx
+++ b/output/pms/Lập_trình_Python/Session 04 - Toán tử số học, logic và Cấu trúc rẽ nhánh/Lesson 03 - Cấu trúc rẽ nhánh điều khiển với if, elif và else/Câu hỏi Quizz/Quizz_Session04_Lesson03.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="65" customWidth="1" min="1" max="1"/>
@@ -483,17 +483,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Hệ thống quản lý bán hàng thực thi đoạn mã Python sau để tính phí vận chuyển:
-```python
-order_amount = 1000000
-if order_amount &gt; 2000000:
-    shipping_fee = 0
-elif order_amount &gt; 1000000:
-    shipping_fee = 15000
-else:
-    shipping_fee = 30000
-```
-Biến `shipping_fee` sẽ lưu giá trị nào sau khi hoàn tất xử lý?</t>
+          <t>Câu 1 (Định nghĩa/Cú pháp): Bạn đang phát triển tính năng tính tiền ShopeeFood. Cú pháp nào sau đây mở đầu đúng cho một khối rẽ nhánh kiểm tra giá trị đơn hàng hợp lệ (lớn hơn 0) trong Python?</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
@@ -501,7 +491,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>shipping_fee = 30000</t>
+          <t>if order_amount &gt; 0:</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -515,45 +505,35 @@
       <c r="B3" s="4" t="n"/>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>shipping_fee = 15000</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr"/>
+          <t>if order_amount &gt; 0 then</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n"/>
       <c r="B4" s="4" t="n"/>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>shipping_fee = 0</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr"/>
+          <t>if (order_amount &gt; 0) {</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n"/>
       <c r="B5" s="4" t="n"/>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>shipping_fee = 1000000</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr"/>
+          <t>check order_amount &gt; 0:</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Trong mô-đun tính chiết khấu cho khách hàng, chương trình Python có đoạn mã:
-```python
-order_amount = 800000
-if order_amount &gt;= 2000000:
-    discount = 0.15
-elif order_amount &gt;= 1000000:
-    discount = 0.10
-else:
-    discount = 0.0
-```
-Giá trị của biến `discount` thu được là bao nhiêu?</t>
+          <t>Câu 2 (Luồng thực thi): Trong chuỗi câu lệnh rẽ nhánh if-elif-else phân loại giảm giá đơn hàng ShopeeFood, nếu điều kiện ở nhánh `if` đầu tiên đã trả về True, luồng thực thi của Python sẽ xử lý như thế nào?</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
@@ -561,58 +541,49 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0.15</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr"/>
+          <t>Thực thi khối lệnh của if rồi thoát ngay khỏi toàn bộ cấu trúc if-elif-else</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n"/>
       <c r="B7" s="4" t="n"/>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0.10</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr"/>
+          <t>Tiếp tục kiểm tra lần lượt tất cả các nhánh elif phía dưới</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n"/>
       <c r="B8" s="4" t="n"/>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
+          <t>Quay lại kiểm tra lại điều kiện if thêm một lần nữa</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n"/>
       <c r="B9" s="4" t="n"/>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0.05</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr"/>
+          <t>Bắt buộc thực thi luôn khối lệnh mặc định trong nhánh else</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Xét đoạn mã kiểm tra điều kiện sử dụng các câu lệnh `if` độc lập dưới đây:
-```python
-order_amount = 2500000
-shipping_fee = 30000
-if order_amount &gt;= 1000000:
-    shipping_fee = 15000
-if order_amount &gt;= 2000000:
-    shipping_fee = 0
-```
-Kết quả cuối cùng của biến `shipping_fee` sau khi đoạn mã thực thi là bao nhiêu?</t>
+          <t>Câu 3 (Đoạn mã mẫu): Cho đoạn mã Python: `order_amount = 250000; is_vip = True`. Nếu kiểm tra điều kiện `if is_vip or order_amount &gt;= 300000: shipping_fee = 0 else: shipping_fee = 15000`, giá trị của `shipping_fee` là bao nhiêu?</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
@@ -620,54 +591,49 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>15000</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr"/>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n"/>
       <c r="B11" s="4" t="n"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>30000</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr"/>
+          <t>15000</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n"/>
       <c r="B12" s="4" t="n"/>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Báo lỗi SyntaxError do khai báo trùng lặp lệnh if</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr"/>
+          <t>250000</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n"/>
       <c r="B13" s="4" t="n"/>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
+          <t>Báo lỗi SyntaxError</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Phát hiện lỗi cú pháp trong câu lệnh rẽ nhánh Python sau đây:
-```python
-if order_amount &gt;= 1000000
-    print("Đơn hàng đủ điều kiện áp dụng ưu đãi")
-```
-Nguyên nhân phát sinh lỗi SyntaxError ở đoạn mã trên là gì?</t>
+          <t>Câu 4 (Phân biệt/So sánh): Điểm khác biệt lớn nhất về mặt logic giữa việc dùng 2 câu lệnh `if` độc lập với dùng 1 cấu trúc `if-elif` khi kiểm tra mốc giá trị đơn hàng là gì?</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
@@ -675,44 +641,94 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Tên biến order_amount không đúng quy tắc đặt tên của Python</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr"/>
+          <t>Hai câu lệnh `if` độc lập luôn kiểm tra cả 2 điều kiện; còn `if-elif` bỏ qua `elif` nếu `if` đã đúng</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n"/>
       <c r="B15" s="4" t="n"/>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Thiếu dấu hai chấm (:) ở cuối dòng chứa điều kiện if</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
+          <t>Hai câu lệnh `if` độc lập chỉ chạy được trên môi trường Linux</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n"/>
       <c r="B16" s="4" t="n"/>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Lệnh print không được phép viết trong khối lệnh của cấu trúc rẽ nhánh</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr"/>
+          <t>Cấu trúc `if-elif` bắt buộc phải có nhánh `else` ở cuối cùng</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n"/>
       <c r="B17" s="4" t="n"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Biểu thức so sánh order_amount &gt;= 1000000 bắt buộc phải bọc trong ngoặc tròn</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr"/>
+          <t>Không có sự khác biệt nào về luồng chạy giữa 2 cách viết</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Câu 5 (Dự đoán kết quả có bẫy): Lập trình viên viết nhầm thứ tự mốc giảm giá: `if order_amount &gt;= 150000: discount = 20000 elif order_amount &gt;= 300000: discount = 50000`. Nếu đơn hàng có giá trị `order_amount = 350000`, bẫy lỗi (Pitfall) nào sẽ xảy ra?</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Khách hàng chỉ được giảm 20,000đ thay vì 50,000đ do nhánh &gt;= 150k đã giữ chân luồng chạy</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n"/>
+      <c r="B19" s="4" t="n"/>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Chương trình bị crash do báo lỗi Unreachable Code Exception</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n"/>
+      <c r="B20" s="4" t="n"/>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Khách hàng được cộng dồn cả 2 mức giảm giá thành 70,000đ</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n"/>
+      <c r="B21" s="4" t="n"/>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Python tự động đảo lại thứ tự câu lệnh để ưu tiên mốc 300,000đ</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
